--- a/spec-tech/ig/StructureDefinition-xdmSourcePatientId.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmSourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T14:32:10+00:00</t>
+    <t>2026-07-23T16:03:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -256,27 +256,28 @@
     <t>1</t>
   </si>
   <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Identifiant du patient, en l’occurrence, le matricule INS du patient tel que défini dans le cadre juridique</t>
-  </si>
-  <si>
-    <t>xdmSourcePatientId.CX4</t>
-  </si>
-  <si>
     <t xml:space="preserve">string
 </t>
   </si>
   <si>
-    <t>Identifiant de l’autorité d’affectation de l’INS utilisé.</t>
+    <t>Identifiant secondaire du patient, en l’occurrence. Equivalent à PatientId s'il n'y a pas d'identifiant secondaire.</t>
+  </si>
+  <si>
+    <t>xdmSourcePatientId.CX4</t>
+  </si>
+  <si>
+    <t>Identifiant de l’autorité d’affectation de l'identifiant utilisé.</t>
+  </si>
+  <si>
+    <t>Cet identifiant, au format HL7 v.2.5 est constitué de trois sous-composants qui prennent les valeurs suivantes en fonction du type d'identifiant.
+INS : Valeur de Namespace ID (IS) = Vide, pas de valeur | Valeur de Universal ID (ST) = OID de l’autorité d’affectation de l’INS utilisé, prise dans la liste des OID des autorités d'affectation des INS | Valeur de Universal ID type (ID) = ISO
+Autre identifiant : Valeur de Namespace ID (IS) = Vide, pas de valeur | Valeur de Universal ID (ST) = OID de l’autorité d’affectation dl'identifiant (i.e. l'instituion qui a attribué cet identifiant) | Valeur de Universal ID type (ID) = ISO</t>
   </si>
   <si>
     <t>xdmSourcePatientId.CX5</t>
   </si>
   <si>
-    <t>'NH' pour un maticule INS tel que défini dans le cadre juridique</t>
+    <t>'NH' pour les patients identifiés par leur INS, 'PI' pour les patients identifiés par d'autres identifiants.</t>
   </si>
 </sst>
 </file>
@@ -591,7 +592,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="7.9765625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="7.6796875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -956,10 +957,10 @@
         <v>73</v>
       </c>
       <c r="K4" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L4" t="s" s="2">
         <v>83</v>
-      </c>
-      <c r="L4" t="s" s="2">
-        <v>84</v>
       </c>
       <c r="M4" t="s" s="2">
         <v>84</v>
@@ -1056,7 +1057,7 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="L5" t="s" s="2">
         <v>86</v>

--- a/spec-tech/ig/StructureDefinition-xdmSourcePatientId.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmSourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:03:49+00:00</t>
+    <t>2026-07-23T16:11:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmSourcePatientId.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmSourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T16:11:23+00:00</t>
+    <t>2026-07-27T13:36:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,11 @@
     <t>Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Cette métadonnée contient l’identifiant secondaire du patient dans le système d’information du producteur (IPP) ou l’INS, s’il n’y a pas d’identifiant secondaire. Pour les documents d’expression personnelle du patient, cette métadonnée contient l’INS du patient, à savoir le même identifiant que patientId. </t>
+    <t xml:space="preserve">Cette métadonnée contient l’identifiant secondaire du patient dans le système d’information du producteur (IPP) ou l’INS, s’il n’y a pas d’identifiant secondaire. Pour les documents d’expression personnelle du patient, cette métadonnée contient l’INS du patient, à savoir le même identifiant que patientId. 
+Cette métadonnée reprend la structure du segment CX  défini par  HL7v2  et  conformément aux spécifications  : 
+- [Prise en Charge de l'INS dans les volets du CI-SIS ](https://esante.gouv.fr/annexe-prise-en-charge-de-lins-dans-les-volets-du-ci-sis)
+- [Volet Partage de Documents de Santé](https://esante.gouv.fr/volet-partage-de-documents-de-sante)
+</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/spec-tech/ig/StructureDefinition-xdmSourcePatientId.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmSourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T13:36:25+00:00</t>
+    <t>2026-07-30T09:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmSourcePatientId.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmSourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:32:03+00:00</t>
+    <t>2026-07-30T15:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/spec-tech/ig/StructureDefinition-xdmSourcePatientId.xlsx
+++ b/spec-tech/ig/StructureDefinition-xdmSourcePatientId.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:04:16+00:00</t>
+    <t>2026-08-07T08:28:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -254,7 +254,7 @@
     <t>Base</t>
   </si>
   <si>
-    <t>xdmSourcePatientId.CX1</t>
+    <t>xdmSourcePatientId.cx1</t>
   </si>
   <si>
     <t>1</t>
@@ -267,7 +267,7 @@
     <t>Identifiant secondaire du patient, en l’occurrence. Equivalent à PatientId s'il n'y a pas d'identifiant secondaire.</t>
   </si>
   <si>
-    <t>xdmSourcePatientId.CX4</t>
+    <t>xdmSourcePatientId.cx4</t>
   </si>
   <si>
     <t>Identifiant de l’autorité d’affectation de l'identifiant utilisé.</t>
@@ -278,7 +278,7 @@
 Autre identifiant : Valeur de Namespace ID (IS) = Vide, pas de valeur | Valeur de Universal ID (ST) = OID de l’autorité d’affectation dl'identifiant (i.e. l'instituion qui a attribué cet identifiant) | Valeur de Universal ID type (ID) = ISO</t>
   </si>
   <si>
-    <t>xdmSourcePatientId.CX5</t>
+    <t>xdmSourcePatientId.cx5</t>
   </si>
   <si>
     <t>'NH' pour les patients identifiés par leur INS, 'PI' pour les patients identifiés par d'autres identifiants.</t>
@@ -586,8 +586,8 @@
   <dimension ref="A1:AJ5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="20.46484375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="20.46484375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="20.0859375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="20.0859375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -617,7 +617,7 @@
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="20.46484375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="20.0859375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
